--- a/parameters/UA/ammonia/technology_parameters.xlsx
+++ b/parameters/UA/ammonia/technology_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samiyhanaqvi/Desktop/SHIELD/restructuring_and_integration/GeoX/parameters/NA/ammonia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DD74D0-2818-854C-90A4-4499A49EEB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D055C2-4FAB-4A8E-A3E1-A51C7CBF2C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10100" yWindow="740" windowWidth="19300" windowHeight="17240" xr2:uid="{C2021D4B-F101-9446-A40F-20FC94B0106D}"/>
+    <workbookView xWindow="3630" yWindow="4350" windowWidth="16770" windowHeight="9330" activeTab="1" xr2:uid="{C2021D4B-F101-9446-A40F-20FC94B0106D}"/>
   </bookViews>
   <sheets>
     <sheet name="Water" sheetId="6" r:id="rId1"/>
@@ -433,17 +433,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F260B15A-B8F5-44FB-9EF4-FDC040BBCD83}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -451,7 +451,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -459,7 +459,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -467,15 +467,15 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -492,13 +492,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F43247-4FF6-844F-9F39-98135821A884}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -520,7 +520,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -533,7 +533,7 @@
         <v>7149.7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
